--- a/reports/Debug-purgatory-20260106/For The Week Ending (Prior Year)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260106/For The Week Ending (Prior Year)_Visits.xlsx
@@ -34,6 +34,9 @@
     <t>Purgatory Passes</t>
   </si>
   <si>
+    <t>Purgatory Coaster</t>
+  </si>
+  <si>
     <t>Purgatory Tickets</t>
   </si>
   <si>
@@ -41,9 +44,6 @@
   </si>
   <si>
     <t>Purgatory Uplift Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Coaster</t>
   </si>
 </sst>
 </file>
@@ -434,10 +434,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C2" s="2">
-        <v>751</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C3" s="2">
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -465,7 +465,7 @@
         <v>45663</v>
       </c>
       <c r="C4" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -476,13 +476,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C5" s="2">
-        <v>1069</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,13 +490,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C6" s="2">
-        <v>1071</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,13 +504,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -521,7 +521,7 @@
         <v>45663</v>
       </c>
       <c r="C8" s="2">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -535,7 +535,7 @@
         <v>45664</v>
       </c>
       <c r="C9" s="2">
-        <v>219</v>
+        <v>1069</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>7</v>
@@ -546,13 +546,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C10" s="2">
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -563,7 +563,7 @@
         <v>45664</v>
       </c>
       <c r="C11" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -577,7 +577,7 @@
         <v>45664</v>
       </c>
       <c r="C12" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -588,10 +588,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C13" s="2">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -605,10 +605,10 @@
         <v>45663</v>
       </c>
       <c r="C14" s="2">
-        <v>6</v>
+        <v>1071</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -619,7 +619,7 @@
         <v>45663</v>
       </c>
       <c r="C15" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -633,7 +633,7 @@
         <v>45663</v>
       </c>
       <c r="C16" s="2">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>5</v>
@@ -647,10 +647,10 @@
         <v>45664</v>
       </c>
       <c r="C17" s="2">
-        <v>5</v>
+        <v>219</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -661,7 +661,7 @@
         <v>45664</v>
       </c>
       <c r="C18" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>9</v>
@@ -672,10 +672,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C19" s="2">
-        <v>4</v>
+        <v>751</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -689,7 +689,7 @@
         <v>45664</v>
       </c>
       <c r="C20" s="2">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -700,13 +700,13 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C21" s="2">
-        <v>9</v>
+        <v>238</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,10 +714,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C22" s="2">
-        <v>2</v>
+        <v>899</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>5</v>
@@ -728,13 +728,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C23" s="2">
-        <v>238</v>
+        <v>132</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,10 +742,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C24" s="2">
-        <v>899</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>5</v>
@@ -759,7 +759,7 @@
         <v>45664</v>
       </c>
       <c r="C25" s="2">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>5</v>
